--- a/Day1-Personal_Expense_Tracker.xlsx
+++ b/Day1-Personal_Expense_Tracker.xlsx
@@ -1,27 +1,176 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Excel\Excel-Practice\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63614337-3A41-4434-857B-277BF1A26E3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="40">
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Payment Mode</t>
+  </si>
+  <si>
+    <t>Amount</t>
+  </si>
+  <si>
+    <t>Food</t>
+  </si>
+  <si>
+    <t>Lunch</t>
+  </si>
+  <si>
+    <t>UPI</t>
+  </si>
+  <si>
+    <t>Transport</t>
+  </si>
+  <si>
+    <t>Auto</t>
+  </si>
+  <si>
+    <t>Cash</t>
+  </si>
+  <si>
+    <t>Shopping</t>
+  </si>
+  <si>
+    <t>T-Shirt</t>
+  </si>
+  <si>
+    <t>Card</t>
+  </si>
+  <si>
+    <t>Pizza</t>
+  </si>
+  <si>
+    <t>Fuel</t>
+  </si>
+  <si>
+    <t>Petrol</t>
+  </si>
+  <si>
+    <t>Entertainment</t>
+  </si>
+  <si>
+    <t>Movie</t>
+  </si>
+  <si>
+    <t>Coffee</t>
+  </si>
+  <si>
+    <t>Metro</t>
+  </si>
+  <si>
+    <t>Dinner</t>
+  </si>
+  <si>
+    <t>Shoes</t>
+  </si>
+  <si>
+    <t>Netflix</t>
+  </si>
+  <si>
+    <t>Breakfast</t>
+  </si>
+  <si>
+    <t>Cab</t>
+  </si>
+  <si>
+    <t>Books</t>
+  </si>
+  <si>
+    <t>Snacks</t>
+  </si>
+  <si>
+    <t>Cricket Match</t>
+  </si>
+  <si>
+    <t>FIND Total expenses</t>
+  </si>
+  <si>
+    <t>Average expense</t>
+  </si>
+  <si>
+    <t>Highest expense</t>
+  </si>
+  <si>
+    <t>Lowest expense</t>
+  </si>
+  <si>
+    <t>Total number of transactions</t>
+  </si>
+  <si>
+    <t>Metrics</t>
+  </si>
+  <si>
+    <t>Total Expense</t>
+  </si>
+  <si>
+    <t>Average Expense</t>
+  </si>
+  <si>
+    <t>Highest</t>
+  </si>
+  <si>
+    <t>Lowest</t>
+  </si>
+  <si>
+    <t>Total Txns</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -49,8 +198,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -330,10 +492,1007 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:T55"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="3">
+        <f>DATE(2026,6,1)</f>
+        <v>46174</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="4">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="3">
+        <v>46174</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="4">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="3">
+        <v>46175</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="4">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="3">
+        <v>46175</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" s="4">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="3">
+        <v>46176</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="4">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="3">
+        <v>46176</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" s="4">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="3">
+        <v>46177</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" s="4">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="3">
+        <v>46177</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E9" s="4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="3">
+        <v>46178</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" s="4">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="3">
+        <v>46178</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11" s="4">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="3">
+        <v>46179</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" s="4">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A13" s="3">
+        <v>46179</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E13" s="4">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="3">
+        <v>46180</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E14" s="4">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="3">
+        <v>46180</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E15" s="4">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="3">
+        <v>46181</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E16" s="4">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A17" s="3">
+        <v>46181</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E17" s="4">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A18" s="3">
+        <v>46182</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E18" s="4">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A19" s="3">
+        <v>46182</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E19" s="4">
+        <v>300</v>
+      </c>
+      <c r="I19" s="5"/>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A20" s="3">
+        <v>46183</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E20" s="4">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A21" s="3">
+        <v>46183</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E21" s="4">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A22" s="2">
+        <v>46184</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E22" s="4">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A23" s="2">
+        <v>46184</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E23" s="4">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A24" s="2">
+        <v>46185</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E24" s="4">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A25" s="2">
+        <v>46186</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E25" s="4">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A26" s="2">
+        <v>46186</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E26" s="4">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A27" s="2">
+        <v>46187</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E27" s="4">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A28" s="2">
+        <v>46187</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E28" s="4">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A29" s="2">
+        <v>46188</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E29" s="4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A30" s="2">
+        <v>46188</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E30" s="4">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A31" s="2">
+        <v>46189</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E31" s="4">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A32" s="2">
+        <v>46189</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E32" s="4">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A33" s="2">
+        <v>46190</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E33" s="4">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A34" s="2">
+        <v>46190</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E34" s="4">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A35" s="2">
+        <v>46191</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E35" s="4">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A36" s="2">
+        <v>46191</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E36" s="4">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A37" s="2">
+        <v>46192</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E37" s="4">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A38" s="2">
+        <v>46192</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E38" s="4">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A39" s="2">
+        <v>46193</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E39" s="4">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A40" s="2">
+        <v>46193</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E40" s="4">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A41" s="2">
+        <v>46194</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E41" s="4">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A42" s="2">
+        <v>46194</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E42" s="4">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A43" s="2">
+        <v>46195</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E43" s="4">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A44" s="2">
+        <v>46195</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E44" s="4">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A45" s="2">
+        <v>46196</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E45" s="4">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A46" s="2">
+        <v>46196</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E46" s="4">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A47" s="2">
+        <v>46197</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E47" s="4">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A48" s="2">
+        <v>46197</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E48" s="4">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="49" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A49" s="2">
+        <v>46198</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E49" s="4">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="50" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A50" s="2">
+        <v>46198</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E50" s="4">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="51" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T51" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="52" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T52" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="53" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T53" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="54" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T54" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="55" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T55" t="s">
+        <v>33</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53E88C7A-8ECF-4212-B489-980E852FD242}">
+  <dimension ref="A1:B13"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="14.77734375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2">
+        <f>SUM(Sheet1!E2:E50)</f>
+        <v>20288</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B3">
+        <f>AVERAGE(Sheet1!E2:'Sheet1'!E50)</f>
+        <v>414.0408163265306</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4">
+        <f>MAX(Sheet1!E2:'Sheet1'!E50)</f>
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B5">
+        <f>MIN(Sheet1!E2:'Sheet1'!E50)</f>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B6">
+        <f>COUNT(Sheet1!E2:'Sheet1'!E50)</f>
+        <v>49</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9">
+        <f>SUMIF(Sheet1!B2:'Sheet1'!B50,"Food",Sheet1!E2:E50)</f>
+        <v>2920</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10">
+        <f>SUMIF(Sheet1!B2:'Sheet1'!B50,"Transport",Sheet1!E2:E50)</f>
+        <v>1370</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11">
+        <f>SUMIF(Sheet1!B2:'Sheet1'!B50,"Shopping",Sheet1!E2:E50)</f>
+        <v>6500</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12">
+        <f>SUMIF(Sheet1!B2:'Sheet1'!B50,"Fuel",Sheet1!E2:E50)</f>
+        <v>7700</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13">
+        <f>SUMIF(Sheet1!B2:'Sheet1'!B50,"Entertainment",Sheet1!E2:E50)</f>
+        <v>1798</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>